--- a/inst/cprd/lsoa_pat.xlsx
+++ b/inst/cprd/lsoa_pat.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="patient_2019_imd.txt" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t xml:space="preserve">Column name</t>
   </si>
@@ -442,34 +442,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -615,7 +615,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="41.45"/>
@@ -636,7 +636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -675,6 +675,20 @@
         <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -697,7 +711,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="41.45"/>
@@ -718,7 +732,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -805,7 +819,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="11.53"/>
   </cols>
@@ -824,7 +838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -838,7 +852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -852,7 +866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -866,7 +880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -880,7 +894,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -894,7 +908,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -908,7 +922,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -922,7 +936,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
@@ -936,7 +950,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -950,7 +964,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -964,7 +978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -978,7 +992,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
@@ -992,7 +1006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>42</v>
       </c>
@@ -1006,7 +1020,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
@@ -1020,7 +1034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -1034,7 +1048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
@@ -1048,7 +1062,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>50</v>
       </c>
@@ -1062,7 +1076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>52</v>
       </c>
@@ -1076,7 +1090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>54</v>
       </c>
@@ -1104,7 +1118,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -1118,7 +1132,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>60</v>
       </c>
@@ -1132,7 +1146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>62</v>
       </c>
@@ -1146,7 +1160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
@@ -1160,7 +1174,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>66</v>
       </c>
@@ -1174,7 +1188,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>68</v>
       </c>
@@ -1188,7 +1202,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>70</v>
       </c>
@@ -1202,7 +1216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>72</v>
       </c>
@@ -1216,7 +1230,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>74</v>
       </c>
@@ -1248,7 +1262,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16380" style="1" width="11.53"/>
   </cols>
@@ -1267,7 +1281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1281,7 +1295,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1354,7 +1368,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16380" style="1" width="11.53"/>
   </cols>
@@ -1373,7 +1387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1387,7 +1401,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1460,7 +1474,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="11.53"/>
@@ -1480,7 +1494,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1494,7 +1508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
